--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Microschool_With_Decisions.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Microschool_With_Decisions.xlsx
@@ -29,7 +29,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated April 29, 2026 · llc_single</t>
+    <t>Generated May 1, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -143,7 +143,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated April 29, 2026</t>
+    <t>Generated May 1, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Microschool_With_Decisions.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Microschool_With_Decisions.xlsx
@@ -29,7 +29,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated May 1, 2026 · llc_single</t>
+    <t>Generated May 7, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -143,7 +143,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated May 1, 2026</t>
+    <t>Generated May 7, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -613,7 +613,7 @@
   </si>
   <si>
     <t xml:space="preserve">• Enrollment -8 cumulative
-• Tuition $-500/student</t>
+• Tuition -$500/student</t>
   </si>
   <si>
     <t>Board declined; enrollment goals retained as originally modeled.</t>
@@ -2129,7 +2129,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:H40"/>
+  <dimension ref="B2:I40"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="4" customWidth="1"/>
@@ -2139,7 +2139,7 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" ht="30" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
         <v>200</v>
       </c>
@@ -2149,8 +2149,9 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B3" s="12" t="s">
         <v>40</v>
       </c>
@@ -2160,6 +2161,7 @@
       <c r="F3" s="12"/>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
+      <c r="I3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="51" t="s">
@@ -2650,7 +2652,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="29" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B29" s="54" t="s">
         <v>231</v>
       </c>
@@ -2666,8 +2668,9 @@
       </c>
       <c r="G29" s="54"/>
       <c r="H29" s="54"/>
-    </row>
-    <row r="30" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I29" s="54"/>
+    </row>
+    <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B30" s="65" t="s">
         <v>235</v>
       </c>
@@ -2683,8 +2686,9 @@
       </c>
       <c r="G30" s="68"/>
       <c r="H30" s="68"/>
-    </row>
-    <row r="31" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I30" s="68"/>
+    </row>
+    <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B31" s="65" t="s">
         <v>239</v>
       </c>
@@ -2700,8 +2704,9 @@
       </c>
       <c r="G31" s="68"/>
       <c r="H31" s="68"/>
-    </row>
-    <row r="32" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I31" s="68"/>
+    </row>
+    <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B32" s="65" t="s">
         <v>242</v>
       </c>
@@ -2717,8 +2722,9 @@
       </c>
       <c r="G32" s="68"/>
       <c r="H32" s="68"/>
-    </row>
-    <row r="33" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I32" s="68"/>
+    </row>
+    <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B33" s="65" t="s">
         <v>245</v>
       </c>
@@ -2734,8 +2740,9 @@
       </c>
       <c r="G33" s="68"/>
       <c r="H33" s="68"/>
-    </row>
-    <row r="34" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I33" s="68"/>
+    </row>
+    <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B34" s="65" t="s">
         <v>249</v>
       </c>
@@ -2751,8 +2758,9 @@
       </c>
       <c r="G34" s="68"/>
       <c r="H34" s="68"/>
-    </row>
-    <row r="35" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I34" s="68"/>
+    </row>
+    <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B35" s="65" t="s">
         <v>252</v>
       </c>
@@ -2768,8 +2776,9 @@
       </c>
       <c r="G35" s="68"/>
       <c r="H35" s="68"/>
-    </row>
-    <row r="36" ht="45" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="I35" s="68"/>
+    </row>
+    <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B36" s="65" t="s">
         <v>256</v>
       </c>
@@ -2785,6 +2794,7 @@
       </c>
       <c r="G36" s="68"/>
       <c r="H36" s="68"/>
+      <c r="I36" s="68"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B38" s="65" t="s">
@@ -2797,7 +2807,7 @@
       <c r="E38" s="28"/>
       <c r="F38" s="28"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B40" s="71" t="s">
         <v>260</v>
       </c>
@@ -2807,29 +2817,30 @@
       <c r="F40" s="71"/>
       <c r="G40" s="71"/>
       <c r="H40" s="71"/>
+      <c r="I40" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="B2:H2"/>
-    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="B3:I3"/>
     <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F29:I29"/>
     <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F30:I30"/>
     <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F31:I31"/>
     <mergeCell ref="D32:E32"/>
-    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="F32:I32"/>
     <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="F33:I33"/>
     <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F34:I34"/>
     <mergeCell ref="D35:E35"/>
-    <mergeCell ref="F35:H35"/>
+    <mergeCell ref="F35:I35"/>
     <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:H36"/>
+    <mergeCell ref="F36:I36"/>
     <mergeCell ref="C38:F38"/>
-    <mergeCell ref="B40:H40"/>
+    <mergeCell ref="B40:I40"/>
   </mergeCells>
   <conditionalFormatting sqref="C12:G12">
     <cfRule type="expression" dxfId="0" priority="1">
@@ -3221,7 +3232,7 @@
         <v>65</v>
       </c>
       <c r="D26" s="22">
-        <v>0.95</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="3:4" x14ac:dyDescent="0.25">

--- a/artifacts/api-server/qa-output/Lender_Pro_Forma_Microschool_With_Decisions.xlsx
+++ b/artifacts/api-server/qa-output/Lender_Pro_Forma_Microschool_With_Decisions.xlsx
@@ -10,18 +10,20 @@
     <sheet sheetId="4" name="Drivers" state="visible" r:id="rId7"/>
     <sheet sheetId="5" name="5-Year P&amp;L" state="visible" r:id="rId8"/>
     <sheet sheetId="6" name="Cash Flow &amp; DSCR" state="visible" r:id="rId9"/>
-    <sheet sheetId="7" name="Staffing" state="visible" r:id="rId10"/>
-    <sheet sheetId="8" name="Loan Snapshot" state="visible" r:id="rId11"/>
-    <sheet sheetId="9" name="Summary" state="visible" r:id="rId12"/>
-    <sheet sheetId="10" name="Decision History" state="visible" r:id="rId13"/>
-    <sheet sheetId="11" name="Financial Health" state="visible" r:id="rId14"/>
+    <sheet sheetId="7" name="AR &amp; Restricted Recon" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="Staffing" state="visible" r:id="rId11"/>
+    <sheet sheetId="9" name="Loan Snapshot" state="visible" r:id="rId12"/>
+    <sheet sheetId="10" name="Summary" state="visible" r:id="rId13"/>
+    <sheet sheetId="11" name="Stress Tests" state="visible" r:id="rId14"/>
+    <sheet sheetId="12" name="Decision History" state="visible" r:id="rId15"/>
+    <sheet sheetId="13" name="Financial Health" state="visible" r:id="rId16"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="261">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="501" uniqueCount="295">
   <si>
     <t>How to Use This Workbook</t>
   </si>
@@ -29,7 +31,7 @@
     <t>Bright Horizons Microschool</t>
   </si>
   <si>
-    <t>Generated May 7, 2026 · llc_single</t>
+    <t>Generated May 9, 2026 · llc_single</t>
   </si>
   <si>
     <t>Cell Color Legend</t>
@@ -143,7 +145,7 @@
     <t>Summary</t>
   </si>
   <si>
-    <t>Generated May 7, 2026</t>
+    <t>Generated May 9, 2026</t>
   </si>
   <si>
     <t>Generated by SchoolStack Budget  •  budget.schoolstack.ai</t>
@@ -398,7 +400,10 @@
     <t>Operating Margin</t>
   </si>
   <si>
-    <t>Capital &amp; Debt Service</t>
+    <t>Interest Expense</t>
+  </si>
+  <si>
+    <t>Principal &amp; Capital Outlays</t>
   </si>
   <si>
     <t>Net Income</t>
@@ -443,6 +448,42 @@
     <t>Ending Cash</t>
   </si>
   <si>
+    <t>AR Schedule &amp; Restricted-vs-Unrestricted Cash Recon</t>
+  </si>
+  <si>
+    <t>AR = year's collected tuition × 30-day weighted delay ÷ 365. Bad debt = contracted − collected.</t>
+  </si>
+  <si>
+    <t>Accounts Receivable Schedule</t>
+  </si>
+  <si>
+    <t>Contracted Tuition (gross)</t>
+  </si>
+  <si>
+    <t>Collected Tuition (cash-basis)</t>
+  </si>
+  <si>
+    <t>Bad Debt (contracted − collected)</t>
+  </si>
+  <si>
+    <t>Year-end AR Balance (30-day delay)</t>
+  </si>
+  <si>
+    <t>Restricted vs Unrestricted Cash</t>
+  </si>
+  <si>
+    <t>Total Cash Position (accrual)</t>
+  </si>
+  <si>
+    <t>Restricted Cash (capital/program-restricted)</t>
+  </si>
+  <si>
+    <t>Unrestricted Cash (DSCR/runway basis)</t>
+  </si>
+  <si>
+    <t>Note: DSCR and cash-runway covenants in this packet are computed off Unrestricted Cash (row 14). Restricted gifts cannot legally service debt and are excluded from coverage tests.</t>
+  </si>
+  <si>
     <t>Staffing Detail</t>
   </si>
   <si>
@@ -507,6 +548,78 @@
   </si>
   <si>
     <t>Generated by SchoolStack Budget (budget.schoolstack.ai)</t>
+  </si>
+  <si>
+    <t>Standard Lender Stress Tests</t>
+  </si>
+  <si>
+    <t>Five fixed downside scenarios re-run on the canonical engine. Identical figures appear on the founder dashboard, consultant view, and lender packet PDF.</t>
+  </si>
+  <si>
+    <t>Scenario</t>
+  </si>
+  <si>
+    <t>Metric</t>
+  </si>
+  <si>
+    <t>Δ vs Base (Y1)</t>
+  </si>
+  <si>
+    <t>Base Case</t>
+  </si>
+  <si>
+    <t>Canonical engine output. All scenarios below are deltas vs this row.</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>DSCR</t>
+  </si>
+  <si>
+    <t>Break-Even Students</t>
+  </si>
+  <si>
+    <t>Cash Runway (mo)</t>
+  </si>
+  <si>
+    <t>Break-Even Year</t>
+  </si>
+  <si>
+    <t>Enrollment -10%</t>
+  </si>
+  <si>
+    <t>All five enrollment years scaled down by 10% — the standard lender enrollment-miss sensitivity.</t>
+  </si>
+  <si>
+    <t>0y</t>
+  </si>
+  <si>
+    <t>Enrollment -20%</t>
+  </si>
+  <si>
+    <t>All five enrollment years scaled down by 20% — the stretch downside lenders use to confirm the school can survive a soft-launch.</t>
+  </si>
+  <si>
+    <t>+1y</t>
+  </si>
+  <si>
+    <t>ESA / Public Funding Delayed 3 Months</t>
+  </si>
+  <si>
+    <t>Year-1 ESA, school-choice, and public-funding receipts reduced by 25% (≈ 3 months delayed) to simulate a slow first disbursement.</t>
+  </si>
+  <si>
+    <t>Rent Shock +25%</t>
+  </si>
+  <si>
+    <t>Occupancy &amp; facility expense rows escalated by 25% — covers a lease renewal, market-rate reset, or unbudgeted CAM/utilities surprise.</t>
+  </si>
+  <si>
+    <t>Founder Comp Normalized to Market</t>
+  </si>
+  <si>
+    <t>Founder compensation re-cast at the market-rate benchmark (with benefits + payroll tax). The lender / board view of true operating cost.</t>
   </si>
   <si>
     <t>Decision History</t>
@@ -588,9 +701,6 @@
     <t>On hold</t>
   </si>
   <si>
-    <t>—</t>
-  </si>
-  <si>
     <t>Mar 25, 2025</t>
   </si>
   <si>
@@ -644,9 +754,6 @@
     <t>○ Red = action needed</t>
   </si>
   <si>
-    <t>Metric</t>
-  </si>
-  <si>
     <t>Benchmark</t>
   </si>
   <si>
@@ -702,9 +809,6 @@
   </si>
   <si>
     <t>≥ 3 sources</t>
-  </si>
-  <si>
-    <t>DSCR</t>
   </si>
   <si>
     <t>≥ 1.25x</t>
@@ -825,7 +929,7 @@
     <numFmt numFmtId="166" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
     <numFmt numFmtId="167" formatCode="0.00x"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -921,6 +1025,18 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <color rgb="FF6B7280"/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
       <color rgb="FF16A34A"/>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -978,12 +1094,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF8E1"/>
+        <fgColor rgb="FFE8EDF2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8EDF2"/>
+        <fgColor rgb="FFFFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -1056,7 +1172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="87">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1120,6 +1236,13 @@
     <xf numFmtId="167" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="16" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="164" fontId="16" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1131,6 +1254,40 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="16" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1152,35 +1309,35 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="166" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="6" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="16" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="167" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1193,7 +1350,7 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1202,13 +1359,13 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1920,6 +2077,1345 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
+  <dimension ref="B1:C21"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>162</v>
+      </c>
+      <c r="C1" s="13"/>
+    </row>
+    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B3" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="25" t="str">
+        <f>Assumptions!D5</f>
+        <v>Bright Horizons Microschool</v>
+      </c>
+    </row>
+    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B4" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C4" s="25" t="str">
+        <f>Assumptions!D7</f>
+        <v>Microschool</v>
+      </c>
+    </row>
+    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B5" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="25" t="str">
+        <f>Assumptions!D6</f>
+        <v>AZ</v>
+      </c>
+    </row>
+    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B6" s="25" t="s">
+        <v>163</v>
+      </c>
+      <c r="C6" s="25">
+        <f>Assumptions!D8</f>
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="C8" s="26">
+        <f>Assumptions!D16</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B9" s="25" t="s">
+        <v>164</v>
+      </c>
+      <c r="C9" s="27">
+        <f>Drivers!G10</f>
+        <v>201964.04175</v>
+      </c>
+    </row>
+    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B10" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C10" s="39">
+        <f>'5-Year P&amp;L'!G16</f>
+        <v>-200501.99456497</v>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B12" s="40" t="s">
+        <v>166</v>
+      </c>
+      <c r="C12" s="23"/>
+    </row>
+    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B13" s="25" t="s">
+        <v>167</v>
+      </c>
+      <c r="C13" s="41">
+        <f>IF(Drivers!G10&gt;0,'5-Year P&amp;L'!G21/Drivers!G10,0)</f>
+        <v>-1.02722149</v>
+      </c>
+    </row>
+    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B14" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="C14" s="31">
+        <f>IF(Drivers!G10&gt;0,Drivers!G16/Drivers!G10,0)</f>
+        <v>1.34416366</v>
+      </c>
+    </row>
+    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B15" s="25" t="s">
+        <v>169</v>
+      </c>
+      <c r="C15" s="27">
+        <f>IF(Assumptions!D16&gt;0,Drivers!G10/Assumptions!D16,0)</f>
+        <v>8079</v>
+      </c>
+    </row>
+    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B16" s="25" t="s">
+        <v>170</v>
+      </c>
+      <c r="C16" s="27">
+        <f>IF(Assumptions!D16&gt;0,('5-Year P&amp;L'!G12+'5-Year P&amp;L'!G13)/Assumptions!D16,0)</f>
+        <v>16099</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="C17" s="34">
+        <f>'Cash Flow &amp; DSCR'!C11</f>
+        <v>-16.26481521</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="25" t="s">
+        <v>172</v>
+      </c>
+      <c r="C18" s="34">
+        <f>'Cash Flow &amp; DSCR'!G11</f>
+        <v>-28.80855028</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="25" t="s">
+        <v>173</v>
+      </c>
+      <c r="C19" s="42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="C21" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B1:C1"/>
+    <mergeCell ref="B21:C21"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FFD97706"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H57"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="38" customWidth="1"/>
+    <col min="2" max="2" width="18" customWidth="1"/>
+    <col min="3" max="8" width="14" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" s="43" t="s">
+        <v>175</v>
+      </c>
+      <c r="B1" s="43"/>
+      <c r="C1" s="43"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+    </row>
+    <row r="2" ht="28" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" s="44" t="s">
+        <v>176</v>
+      </c>
+      <c r="B2" s="44"/>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" s="45" t="s">
+        <v>177</v>
+      </c>
+      <c r="B4" s="45" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="46" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="46" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="46" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" s="46" t="s">
+        <v>99</v>
+      </c>
+      <c r="G4" s="46" t="s">
+        <v>100</v>
+      </c>
+      <c r="H4" s="46" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" s="47" t="s">
+        <v>180</v>
+      </c>
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+    </row>
+    <row r="6" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" s="48" t="s">
+        <v>181</v>
+      </c>
+      <c r="B6" s="48"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C7" s="27">
+        <v>18272.6914494058</v>
+      </c>
+      <c r="D7" s="27">
+        <v>131664.56144940582</v>
+      </c>
+      <c r="E7" s="27">
+        <v>209799.65754940585</v>
+      </c>
+      <c r="F7" s="27">
+        <v>273590.96315740584</v>
+      </c>
+      <c r="G7" s="27">
+        <v>282715.6104492708</v>
+      </c>
+      <c r="H7" s="49" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="C8" s="50">
+        <v>3.63</v>
+      </c>
+      <c r="D8" s="26">
+        <v>19.92</v>
+      </c>
+      <c r="E8" s="26">
+        <v>31.14</v>
+      </c>
+      <c r="F8" s="26">
+        <v>40.31</v>
+      </c>
+      <c r="G8" s="26">
+        <v>41.62</v>
+      </c>
+      <c r="H8" s="49" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C9" s="27">
+        <v>33272.6914494058</v>
+      </c>
+      <c r="D9" s="27">
+        <v>164937.25289881162</v>
+      </c>
+      <c r="E9" s="27">
+        <v>374736.9104482175</v>
+      </c>
+      <c r="F9" s="27">
+        <v>648327.8736056234</v>
+      </c>
+      <c r="G9" s="27">
+        <v>931043.4840548942</v>
+      </c>
+      <c r="H9" s="49" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C10" s="26">
+        <v>11</v>
+      </c>
+      <c r="D10" s="26">
+        <v>11</v>
+      </c>
+      <c r="E10" s="26">
+        <v>11</v>
+      </c>
+      <c r="F10" s="26">
+        <v>11</v>
+      </c>
+      <c r="G10" s="26">
+        <v>11</v>
+      </c>
+      <c r="H10" s="49" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C11" s="26">
+        <v>60</v>
+      </c>
+      <c r="D11" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="F11" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="G11" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="H11" s="52" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="G12" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="H12" s="49" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" s="47" t="s">
+        <v>187</v>
+      </c>
+      <c r="B14" s="47"/>
+      <c r="C14" s="47"/>
+      <c r="D14" s="47"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="47"/>
+      <c r="H14" s="47"/>
+    </row>
+    <row r="15" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" s="48" t="s">
+        <v>188</v>
+      </c>
+      <c r="B15" s="48"/>
+      <c r="C15" s="48"/>
+      <c r="D15" s="48"/>
+      <c r="E15" s="48"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="48"/>
+      <c r="H15" s="48"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C16" s="27">
+        <v>3897.6914494058</v>
+      </c>
+      <c r="D16" s="27">
+        <v>96136.56144940582</v>
+      </c>
+      <c r="E16" s="27">
+        <v>173212.85754940586</v>
+      </c>
+      <c r="F16" s="27">
+        <v>235912.58815740581</v>
+      </c>
+      <c r="G16" s="27">
+        <v>243914.91107427084</v>
+      </c>
+      <c r="H16" s="32">
+        <v>-14375</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="C17" s="50">
+        <v>1.56</v>
+      </c>
+      <c r="D17" s="26">
+        <v>14.81</v>
+      </c>
+      <c r="E17" s="26">
+        <v>25.89</v>
+      </c>
+      <c r="F17" s="26">
+        <v>34.9</v>
+      </c>
+      <c r="G17" s="26">
+        <v>36.05</v>
+      </c>
+      <c r="H17" s="52">
+        <v>-2.07</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C18" s="27">
+        <v>18897.6914494058</v>
+      </c>
+      <c r="D18" s="27">
+        <v>115034.25289881162</v>
+      </c>
+      <c r="E18" s="27">
+        <v>288247.1104482175</v>
+      </c>
+      <c r="F18" s="27">
+        <v>524159.6986056233</v>
+      </c>
+      <c r="G18" s="27">
+        <v>768074.6096798942</v>
+      </c>
+      <c r="H18" s="32">
+        <v>-14375</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A19" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C19" s="26">
+        <v>11</v>
+      </c>
+      <c r="D19" s="26">
+        <v>11</v>
+      </c>
+      <c r="E19" s="26">
+        <v>11</v>
+      </c>
+      <c r="F19" s="26">
+        <v>11</v>
+      </c>
+      <c r="G19" s="26">
+        <v>11</v>
+      </c>
+      <c r="H19" s="52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A20" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C20" s="26">
+        <v>60</v>
+      </c>
+      <c r="D20" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E20" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="F20" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="G20" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="H20" s="52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A21" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C21" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="D21" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E21" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="F21" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="G21" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="H21" s="49" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A23" s="47" t="s">
+        <v>190</v>
+      </c>
+      <c r="B23" s="47"/>
+      <c r="C23" s="47"/>
+      <c r="D23" s="47"/>
+      <c r="E23" s="47"/>
+      <c r="F23" s="47"/>
+      <c r="G23" s="47"/>
+      <c r="H23" s="47"/>
+    </row>
+    <row r="24" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A24" s="48" t="s">
+        <v>191</v>
+      </c>
+      <c r="B24" s="48"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="48"/>
+      <c r="E24" s="48"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="48"/>
+      <c r="H24" s="48"/>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A25" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B25" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C25" s="27">
+        <v>-10477.3085505942</v>
+      </c>
+      <c r="D25" s="27">
+        <v>60608.561449405825</v>
+      </c>
+      <c r="E25" s="27">
+        <v>136626.05754940587</v>
+      </c>
+      <c r="F25" s="27">
+        <v>179395.02565740581</v>
+      </c>
+      <c r="G25" s="27">
+        <v>185713.86201177083</v>
+      </c>
+      <c r="H25" s="32">
+        <v>-28750</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="C26" s="26">
+        <v>-0.51</v>
+      </c>
+      <c r="D26" s="26">
+        <v>9.71</v>
+      </c>
+      <c r="E26" s="26">
+        <v>20.63</v>
+      </c>
+      <c r="F26" s="26">
+        <v>26.78</v>
+      </c>
+      <c r="G26" s="26">
+        <v>27.68</v>
+      </c>
+      <c r="H26" s="52">
+        <v>-4.14</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C27" s="27">
+        <v>4522.6914494058</v>
+      </c>
+      <c r="D27" s="27">
+        <v>65131.252898811625</v>
+      </c>
+      <c r="E27" s="27">
+        <v>201757.3104482175</v>
+      </c>
+      <c r="F27" s="27">
+        <v>381152.3361056233</v>
+      </c>
+      <c r="G27" s="27">
+        <v>566866.1981173941</v>
+      </c>
+      <c r="H27" s="32">
+        <v>-28750</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A28" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C28" s="26">
+        <v>11</v>
+      </c>
+      <c r="D28" s="26">
+        <v>11</v>
+      </c>
+      <c r="E28" s="26">
+        <v>11</v>
+      </c>
+      <c r="F28" s="26">
+        <v>11</v>
+      </c>
+      <c r="G28" s="26">
+        <v>11</v>
+      </c>
+      <c r="H28" s="52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A29" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C29" s="26">
+        <v>6</v>
+      </c>
+      <c r="D29" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E29" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="F29" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="G29" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="H29" s="52">
+        <v>-54</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A30" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C30" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="D30" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E30" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="F30" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="G30" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="H30" s="49" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="47" t="s">
+        <v>193</v>
+      </c>
+      <c r="B32" s="47"/>
+      <c r="C32" s="47"/>
+      <c r="D32" s="47"/>
+      <c r="E32" s="47"/>
+      <c r="F32" s="47"/>
+      <c r="G32" s="47"/>
+      <c r="H32" s="47"/>
+    </row>
+    <row r="33" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A33" s="48" t="s">
+        <v>194</v>
+      </c>
+      <c r="B33" s="48"/>
+      <c r="C33" s="48"/>
+      <c r="D33" s="48"/>
+      <c r="E33" s="48"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="48"/>
+      <c r="H33" s="48"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A34" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C34" s="27">
+        <v>772.6914494058001</v>
+      </c>
+      <c r="D34" s="27">
+        <v>131664.56144940582</v>
+      </c>
+      <c r="E34" s="27">
+        <v>209799.65754940585</v>
+      </c>
+      <c r="F34" s="27">
+        <v>273590.96315740584</v>
+      </c>
+      <c r="G34" s="27">
+        <v>282715.6104492708</v>
+      </c>
+      <c r="H34" s="32">
+        <v>-17500</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="C35" s="54">
+        <v>1.11</v>
+      </c>
+      <c r="D35" s="26">
+        <v>19.92</v>
+      </c>
+      <c r="E35" s="26">
+        <v>31.14</v>
+      </c>
+      <c r="F35" s="26">
+        <v>40.31</v>
+      </c>
+      <c r="G35" s="26">
+        <v>41.62</v>
+      </c>
+      <c r="H35" s="52">
+        <v>-2.5199999999999996</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C36" s="27">
+        <v>15772.6914494058</v>
+      </c>
+      <c r="D36" s="27">
+        <v>147437.25289881162</v>
+      </c>
+      <c r="E36" s="27">
+        <v>357236.9104482175</v>
+      </c>
+      <c r="F36" s="27">
+        <v>630827.8736056234</v>
+      </c>
+      <c r="G36" s="27">
+        <v>913543.4840548942</v>
+      </c>
+      <c r="H36" s="32">
+        <v>-17500</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C37" s="26">
+        <v>12</v>
+      </c>
+      <c r="D37" s="26">
+        <v>11</v>
+      </c>
+      <c r="E37" s="26">
+        <v>11</v>
+      </c>
+      <c r="F37" s="26">
+        <v>11</v>
+      </c>
+      <c r="G37" s="26">
+        <v>11</v>
+      </c>
+      <c r="H37" s="52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A38" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C38" s="26">
+        <v>9</v>
+      </c>
+      <c r="D38" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E38" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="F38" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="G38" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="H38" s="52">
+        <v>-51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A39" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C39" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="F39" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="G39" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="H39" s="49" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="41" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" s="47" t="s">
+        <v>195</v>
+      </c>
+      <c r="B41" s="47"/>
+      <c r="C41" s="47"/>
+      <c r="D41" s="47"/>
+      <c r="E41" s="47"/>
+      <c r="F41" s="47"/>
+      <c r="G41" s="47"/>
+      <c r="H41" s="47"/>
+    </row>
+    <row r="42" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A42" s="48" t="s">
+        <v>196</v>
+      </c>
+      <c r="B42" s="48"/>
+      <c r="C42" s="48"/>
+      <c r="D42" s="48"/>
+      <c r="E42" s="48"/>
+      <c r="F42" s="48"/>
+      <c r="G42" s="48"/>
+      <c r="H42" s="48"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A43" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C43" s="27">
+        <v>10772.6914494058</v>
+      </c>
+      <c r="D43" s="27">
+        <v>122402.06144940582</v>
+      </c>
+      <c r="E43" s="27">
+        <v>200266.97004940585</v>
+      </c>
+      <c r="F43" s="27">
+        <v>263780.17471990583</v>
+      </c>
+      <c r="G43" s="27">
+        <v>272618.5750383333</v>
+      </c>
+      <c r="H43" s="32">
+        <v>-7500</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A44" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="C44" s="50">
+        <v>2.55</v>
+      </c>
+      <c r="D44" s="26">
+        <v>18.59</v>
+      </c>
+      <c r="E44" s="26">
+        <v>29.77</v>
+      </c>
+      <c r="F44" s="26">
+        <v>38.9</v>
+      </c>
+      <c r="G44" s="26">
+        <v>40.17</v>
+      </c>
+      <c r="H44" s="52">
+        <v>-1.08</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A45" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C45" s="27">
+        <v>25772.6914494058</v>
+      </c>
+      <c r="D45" s="27">
+        <v>148174.75289881162</v>
+      </c>
+      <c r="E45" s="27">
+        <v>348441.7229482175</v>
+      </c>
+      <c r="F45" s="27">
+        <v>612221.8976681232</v>
+      </c>
+      <c r="G45" s="27">
+        <v>884840.4727064566</v>
+      </c>
+      <c r="H45" s="32">
+        <v>-7500</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A46" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C46" s="26">
+        <v>12</v>
+      </c>
+      <c r="D46" s="26">
+        <v>12</v>
+      </c>
+      <c r="E46" s="26">
+        <v>12</v>
+      </c>
+      <c r="F46" s="26">
+        <v>12</v>
+      </c>
+      <c r="G46" s="26">
+        <v>12</v>
+      </c>
+      <c r="H46" s="52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A47" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B47" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C47" s="26">
+        <v>60</v>
+      </c>
+      <c r="D47" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E47" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="F47" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="G47" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="H47" s="52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A48" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C48" s="53" t="s">
+        <v>96</v>
+      </c>
+      <c r="D48" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E48" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="F48" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="G48" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="H48" s="49" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="50" ht="18" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A50" s="47" t="s">
+        <v>197</v>
+      </c>
+      <c r="B50" s="47"/>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="47"/>
+      <c r="F50" s="47"/>
+      <c r="G50" s="47"/>
+      <c r="H50" s="47"/>
+    </row>
+    <row r="51" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A51" s="48" t="s">
+        <v>198</v>
+      </c>
+      <c r="B51" s="48"/>
+      <c r="C51" s="48"/>
+      <c r="D51" s="48"/>
+      <c r="E51" s="48"/>
+      <c r="F51" s="48"/>
+      <c r="G51" s="48"/>
+      <c r="H51" s="48"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A52" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="C52" s="27">
+        <v>-874.8085505941999</v>
+      </c>
+      <c r="D52" s="27">
+        <v>112070.28644940583</v>
+      </c>
+      <c r="E52" s="27">
+        <v>189822.43254940584</v>
+      </c>
+      <c r="F52" s="27">
+        <v>253294.61315740584</v>
+      </c>
+      <c r="G52" s="27">
+        <v>260891.2899492708</v>
+      </c>
+      <c r="H52" s="32">
+        <v>-19147.5</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B53" s="25" t="s">
+        <v>183</v>
+      </c>
+      <c r="C53" s="54">
+        <v>0.87</v>
+      </c>
+      <c r="D53" s="26">
+        <v>17.1</v>
+      </c>
+      <c r="E53" s="26">
+        <v>28.27</v>
+      </c>
+      <c r="F53" s="26">
+        <v>37.39</v>
+      </c>
+      <c r="G53" s="26">
+        <v>38.49</v>
+      </c>
+      <c r="H53" s="52">
+        <v>-2.76</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B54" s="25" t="s">
+        <v>140</v>
+      </c>
+      <c r="C54" s="27">
+        <v>33272.6914494058</v>
+      </c>
+      <c r="D54" s="27">
+        <v>164937.25289881162</v>
+      </c>
+      <c r="E54" s="27">
+        <v>374736.9104482175</v>
+      </c>
+      <c r="F54" s="27">
+        <v>648327.8736056234</v>
+      </c>
+      <c r="G54" s="27">
+        <v>931043.4840548942</v>
+      </c>
+      <c r="H54" s="32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A55" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="B55" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C55" s="26">
+        <v>11</v>
+      </c>
+      <c r="D55" s="26">
+        <v>11</v>
+      </c>
+      <c r="E55" s="26">
+        <v>11</v>
+      </c>
+      <c r="F55" s="26">
+        <v>11</v>
+      </c>
+      <c r="G55" s="26">
+        <v>11</v>
+      </c>
+      <c r="H55" s="52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A56" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B56" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="C56" s="26">
+        <v>60</v>
+      </c>
+      <c r="D56" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E56" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="F56" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="G56" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="H56" s="52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A57" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="B57" s="25" t="s">
+        <v>186</v>
+      </c>
+      <c r="C57" s="53" t="s">
+        <v>97</v>
+      </c>
+      <c r="D57" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="E57" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="F57" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="G57" s="51" t="s">
+        <v>7</v>
+      </c>
+      <c r="H57" s="49" t="s">
+        <v>192</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A6:H6"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A23:H23"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A42:H42"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A51:H51"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor rgb="FF328555"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:H11"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
@@ -1935,7 +3431,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>162</v>
+        <v>199</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -1945,162 +3441,162 @@
       <c r="H1" s="13"/>
     </row>
     <row r="2" ht="44" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B2" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
+      <c r="B2" s="55" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
     </row>
     <row r="4" ht="28" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B4" s="41" t="s">
-        <v>164</v>
-      </c>
-      <c r="C4" s="41" t="s">
-        <v>165</v>
-      </c>
-      <c r="D4" s="41" t="s">
-        <v>166</v>
-      </c>
-      <c r="E4" s="41" t="s">
-        <v>167</v>
-      </c>
-      <c r="F4" s="41" t="s">
-        <v>168</v>
-      </c>
-      <c r="G4" s="41" t="s">
-        <v>169</v>
-      </c>
-      <c r="H4" s="41" t="s">
-        <v>170</v>
+      <c r="B4" s="56" t="s">
+        <v>201</v>
+      </c>
+      <c r="C4" s="56" t="s">
+        <v>202</v>
+      </c>
+      <c r="D4" s="56" t="s">
+        <v>203</v>
+      </c>
+      <c r="E4" s="56" t="s">
+        <v>204</v>
+      </c>
+      <c r="F4" s="56" t="s">
+        <v>205</v>
+      </c>
+      <c r="G4" s="56" t="s">
+        <v>206</v>
+      </c>
+      <c r="H4" s="56" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="5" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" s="42"/>
-      <c r="B5" s="43" t="s">
-        <v>171</v>
-      </c>
-      <c r="C5" s="44" t="s">
-        <v>172</v>
-      </c>
-      <c r="D5" s="45" t="s">
-        <v>173</v>
-      </c>
-      <c r="E5" s="44" t="s">
-        <v>174</v>
-      </c>
-      <c r="F5" s="46" t="s">
-        <v>175</v>
-      </c>
-      <c r="G5" s="44" t="s">
-        <v>176</v>
-      </c>
-      <c r="H5" s="44" t="s">
-        <v>177</v>
+      <c r="A5" s="57"/>
+      <c r="B5" s="58" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>209</v>
+      </c>
+      <c r="D5" s="60" t="s">
+        <v>210</v>
+      </c>
+      <c r="E5" s="59" t="s">
+        <v>211</v>
+      </c>
+      <c r="F5" s="61" t="s">
+        <v>212</v>
+      </c>
+      <c r="G5" s="59" t="s">
+        <v>213</v>
+      </c>
+      <c r="H5" s="59" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="42"/>
-      <c r="B6" s="43" t="s">
-        <v>178</v>
-      </c>
-      <c r="C6" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="D6" s="45" t="s">
-        <v>173</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>180</v>
-      </c>
-      <c r="F6" s="46" t="s">
-        <v>181</v>
-      </c>
-      <c r="G6" s="44" t="s">
+      <c r="A6" s="57"/>
+      <c r="B6" s="58" t="s">
+        <v>215</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="D6" s="60" t="s">
+        <v>210</v>
+      </c>
+      <c r="E6" s="59" t="s">
+        <v>217</v>
+      </c>
+      <c r="F6" s="61" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" s="59" t="s">
+        <v>219</v>
+      </c>
+      <c r="H6" s="59" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="7" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" s="62"/>
+      <c r="B7" s="58" t="s">
+        <v>221</v>
+      </c>
+      <c r="C7" s="59" t="s">
+        <v>222</v>
+      </c>
+      <c r="D7" s="63" t="s">
+        <v>223</v>
+      </c>
+      <c r="E7" s="59" t="s">
         <v>182</v>
       </c>
-      <c r="H6" s="44" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="7" ht="64" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" s="47"/>
-      <c r="B7" s="43" t="s">
-        <v>184</v>
-      </c>
-      <c r="C7" s="44" t="s">
-        <v>185</v>
-      </c>
-      <c r="D7" s="48" t="s">
-        <v>186</v>
-      </c>
-      <c r="E7" s="44" t="s">
-        <v>187</v>
-      </c>
-      <c r="F7" s="46" t="s">
-        <v>188</v>
-      </c>
-      <c r="G7" s="44" t="s">
-        <v>189</v>
-      </c>
-      <c r="H7" s="44" t="s">
-        <v>190</v>
+      <c r="F7" s="61" t="s">
+        <v>224</v>
+      </c>
+      <c r="G7" s="59" t="s">
+        <v>225</v>
+      </c>
+      <c r="H7" s="59" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" s="49"/>
-      <c r="B8" s="43" t="s">
-        <v>191</v>
-      </c>
-      <c r="C8" s="44" t="s">
-        <v>179</v>
-      </c>
-      <c r="D8" s="50" t="s">
-        <v>192</v>
-      </c>
-      <c r="E8" s="44" t="s">
-        <v>187</v>
-      </c>
-      <c r="F8" s="46" t="s">
-        <v>193</v>
-      </c>
-      <c r="G8" s="44" t="s">
-        <v>194</v>
-      </c>
-      <c r="H8" s="44" t="s">
-        <v>195</v>
+      <c r="A8" s="64"/>
+      <c r="B8" s="58" t="s">
+        <v>227</v>
+      </c>
+      <c r="C8" s="59" t="s">
+        <v>216</v>
+      </c>
+      <c r="D8" s="65" t="s">
+        <v>228</v>
+      </c>
+      <c r="E8" s="59" t="s">
+        <v>182</v>
+      </c>
+      <c r="F8" s="61" t="s">
+        <v>229</v>
+      </c>
+      <c r="G8" s="59" t="s">
+        <v>230</v>
+      </c>
+      <c r="H8" s="59" t="s">
+        <v>231</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" s="49"/>
-      <c r="B9" s="43" t="s">
-        <v>196</v>
-      </c>
-      <c r="C9" s="44" t="s">
-        <v>185</v>
-      </c>
-      <c r="D9" s="50" t="s">
-        <v>192</v>
-      </c>
-      <c r="E9" s="44" t="s">
-        <v>187</v>
-      </c>
-      <c r="F9" s="46" t="s">
-        <v>197</v>
-      </c>
-      <c r="G9" s="44" t="s">
-        <v>198</v>
-      </c>
-      <c r="H9" s="44" t="s">
-        <v>199</v>
+      <c r="A9" s="64"/>
+      <c r="B9" s="58" t="s">
+        <v>232</v>
+      </c>
+      <c r="C9" s="59" t="s">
+        <v>222</v>
+      </c>
+      <c r="D9" s="65" t="s">
+        <v>228</v>
+      </c>
+      <c r="E9" s="59" t="s">
+        <v>182</v>
+      </c>
+      <c r="F9" s="61" t="s">
+        <v>233</v>
+      </c>
+      <c r="G9" s="59" t="s">
+        <v>234</v>
+      </c>
+      <c r="H9" s="59" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="12" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="C11" s="12"/>
       <c r="D11" s="12"/>
@@ -2123,7 +3619,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF328555"/>
@@ -2141,7 +3637,7 @@
   <sheetData>
     <row r="2" ht="30" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B2" s="1" t="s">
-        <v>200</v>
+        <v>236</v>
       </c>
       <c r="C2" s="1"/>
       <c r="D2" s="1"/>
@@ -2164,37 +3660,37 @@
       <c r="I3" s="12"/>
     </row>
     <row r="4" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B4" s="51" t="s">
-        <v>201</v>
-      </c>
-      <c r="D4" s="52" t="s">
-        <v>202</v>
-      </c>
-      <c r="F4" s="53" t="s">
-        <v>203</v>
+      <c r="B4" s="66" t="s">
+        <v>237</v>
+      </c>
+      <c r="D4" s="67" t="s">
+        <v>238</v>
+      </c>
+      <c r="F4" s="68" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B6" s="54" t="s">
-        <v>204</v>
-      </c>
-      <c r="C6" s="55" t="s">
+      <c r="B6" s="69" t="s">
+        <v>178</v>
+      </c>
+      <c r="C6" s="70" t="s">
         <v>96</v>
       </c>
-      <c r="D6" s="55" t="s">
+      <c r="D6" s="70" t="s">
         <v>97</v>
       </c>
-      <c r="E6" s="55" t="s">
+      <c r="E6" s="70" t="s">
         <v>98</v>
       </c>
-      <c r="F6" s="55" t="s">
+      <c r="F6" s="70" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="55" t="s">
+      <c r="G6" s="70" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="55" t="s">
-        <v>205</v>
+      <c r="H6" s="70" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
@@ -2219,7 +3715,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>206</v>
+        <v>241</v>
       </c>
       <c r="C8" s="27">
         <v>89000</v>
@@ -2239,7 +3735,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="25" t="s">
-        <v>207</v>
+        <v>242</v>
       </c>
       <c r="C9" s="27">
         <v>153600</v>
@@ -2259,7 +3755,7 @@
     </row>
     <row r="10" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B10" s="25" t="s">
-        <v>208</v>
+        <v>243</v>
       </c>
       <c r="C10" s="27">
         <v>48600</v>
@@ -2279,7 +3775,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="25" t="s">
-        <v>209</v>
+        <v>244</v>
       </c>
       <c r="C11" s="27">
         <v>6959.808550594178</v>
@@ -2299,7 +3795,7 @@
     </row>
     <row r="12" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B12" s="28" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C12" s="30">
         <v>-120159.80855059417</v>
@@ -2319,7 +3815,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C13" s="30">
         <v>-120159.80855059417</v>
@@ -2339,50 +3835,50 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>127</v>
-      </c>
-      <c r="C14" s="56">
+        <v>128</v>
+      </c>
+      <c r="C14" s="71">
         <v>-1.3501102084336423</v>
       </c>
-      <c r="D14" s="56">
+      <c r="D14" s="71">
         <v>-1.0023728190428414</v>
       </c>
-      <c r="E14" s="56">
+      <c r="E14" s="71">
         <v>-0.7346884451071656</v>
       </c>
-      <c r="F14" s="56">
+      <c r="F14" s="71">
         <v>-0.8890239721196186</v>
       </c>
-      <c r="G14" s="56">
+      <c r="G14" s="71">
         <v>-1.0272214861513054</v>
       </c>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="28" t="s">
-        <v>210</v>
-      </c>
-      <c r="C15" s="57">
+        <v>245</v>
+      </c>
+      <c r="C15" s="72">
         <v>7416.666666666667</v>
       </c>
-      <c r="D15" s="57">
+      <c r="D15" s="72">
         <v>7487.777777777777</v>
       </c>
-      <c r="E15" s="57">
+      <c r="E15" s="72">
         <v>7653.572727272727</v>
       </c>
-      <c r="F15" s="57">
+      <c r="F15" s="72">
         <v>7849.089</v>
       </c>
-      <c r="G15" s="57">
+      <c r="G15" s="72">
         <v>8078.561670000001</v>
       </c>
-      <c r="H15" s="58" t="s">
-        <v>211</v>
+      <c r="H15" s="73" t="s">
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>212</v>
+        <v>247</v>
       </c>
       <c r="C16" s="32">
         <v>17429.984045882848</v>
@@ -2402,7 +3898,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="25" t="s">
-        <v>213</v>
+        <v>248</v>
       </c>
       <c r="C17" s="27">
         <v>500</v>
@@ -2422,402 +3918,402 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="C18" s="57">
+        <v>249</v>
+      </c>
+      <c r="C18" s="72">
         <v>3000</v>
       </c>
-      <c r="D18" s="57">
+      <c r="D18" s="72">
         <v>2058.666666666667</v>
       </c>
-      <c r="E18" s="59">
+      <c r="E18" s="74">
         <v>1733.7716363636368</v>
       </c>
-      <c r="F18" s="59">
+      <c r="F18" s="74">
         <v>1570.4734651733338</v>
       </c>
-      <c r="G18" s="59">
+      <c r="G18" s="74">
         <v>1616.5406868184184</v>
       </c>
-      <c r="H18" s="58" t="s">
-        <v>215</v>
+      <c r="H18" s="73" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="28" t="s">
-        <v>216</v>
-      </c>
-      <c r="C19" s="36">
+        <v>251</v>
+      </c>
+      <c r="C19" s="39">
         <v>-10013.317379216182</v>
       </c>
-      <c r="D19" s="36">
+      <c r="D19" s="39">
         <v>-7505.544919477454</v>
       </c>
-      <c r="E19" s="36">
+      <c r="E19" s="39">
         <v>-5622.9914465146085</v>
       </c>
-      <c r="F19" s="36">
+      <c r="F19" s="39">
         <v>-6978.028280300405</v>
       </c>
-      <c r="G19" s="36">
+      <c r="G19" s="39">
         <v>-8298.472124622373</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B20" s="28" t="s">
-        <v>217</v>
-      </c>
-      <c r="C20" s="56">
+        <v>252</v>
+      </c>
+      <c r="C20" s="71">
         <v>1.7258426966292135</v>
       </c>
-      <c r="D20" s="56">
+      <c r="D20" s="71">
         <v>1.5085472622050748</v>
       </c>
-      <c r="E20" s="56">
+      <c r="E20" s="71">
         <v>1.2437546101464199</v>
       </c>
-      <c r="F20" s="56">
+      <c r="F20" s="71">
         <v>1.3431660790188518</v>
       </c>
-      <c r="G20" s="56">
+      <c r="G20" s="71">
         <v>1.344163657152598</v>
       </c>
-      <c r="H20" s="58" t="s">
-        <v>218</v>
+      <c r="H20" s="73" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="28" t="s">
-        <v>219</v>
-      </c>
-      <c r="C21" s="56">
+        <v>254</v>
+      </c>
+      <c r="C21" s="71">
         <v>0.4044943820224719</v>
       </c>
-      <c r="D21" s="56">
+      <c r="D21" s="71">
         <v>0.27493693426324384</v>
       </c>
-      <c r="E21" s="56">
+      <c r="E21" s="71">
         <v>0.22653101997522254</v>
       </c>
-      <c r="F21" s="60">
+      <c r="F21" s="75">
         <v>0.20008353392009362</v>
       </c>
-      <c r="G21" s="60">
+      <c r="G21" s="75">
         <v>0.2001025371659282</v>
       </c>
-      <c r="H21" s="58" t="s">
-        <v>220</v>
+      <c r="H21" s="73" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="C22" s="56">
+      <c r="C22" s="71">
         <v>-1.2719101123595506</v>
       </c>
-      <c r="D22" s="56">
+      <c r="D22" s="71">
         <v>-0.9507345303457486</v>
       </c>
-      <c r="E22" s="56">
+      <c r="E22" s="71">
         <v>-0.6933541630155331</v>
       </c>
-      <c r="F22" s="56">
+      <c r="F22" s="71">
         <v>-0.8535558633972221</v>
       </c>
-      <c r="G22" s="56">
+      <c r="G22" s="71">
         <v>-0.99276085399972</v>
       </c>
-      <c r="H22" s="58" t="s">
-        <v>221</v>
+      <c r="H22" s="73" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B23" s="28" t="s">
-        <v>222</v>
-      </c>
-      <c r="C23" s="61">
+        <v>257</v>
+      </c>
+      <c r="C23" s="76">
         <v>2</v>
       </c>
-      <c r="D23" s="61">
+      <c r="D23" s="76">
         <v>2</v>
       </c>
-      <c r="E23" s="61">
+      <c r="E23" s="76">
         <v>2</v>
       </c>
-      <c r="F23" s="61">
+      <c r="F23" s="76">
         <v>2</v>
       </c>
-      <c r="G23" s="61">
+      <c r="G23" s="76">
         <v>2</v>
       </c>
-      <c r="H23" s="58" t="s">
-        <v>223</v>
+      <c r="H23" s="73" t="s">
+        <v>258</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B24" s="28" t="s">
-        <v>224</v>
-      </c>
-      <c r="C24" s="62">
+        <v>183</v>
+      </c>
+      <c r="C24" s="77">
         <v>-16.26481521396674</v>
       </c>
-      <c r="D24" s="62">
+      <c r="D24" s="77">
         <v>-18.411425985138678</v>
       </c>
-      <c r="E24" s="62">
+      <c r="E24" s="77">
         <v>-16.77431245759775</v>
       </c>
-      <c r="F24" s="62">
+      <c r="F24" s="77">
         <v>-24.065446231651993</v>
       </c>
-      <c r="G24" s="62">
+      <c r="G24" s="77">
         <v>-28.808550279425102</v>
       </c>
-      <c r="H24" s="58" t="s">
-        <v>225</v>
+      <c r="H24" s="73" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B25" s="28" t="s">
-        <v>226</v>
-      </c>
-      <c r="C25" s="63" t="str">
+        <v>260</v>
+      </c>
+      <c r="C25" s="78" t="str">
         <f>IF('5-Year P&amp;L'!C24&gt;=0,"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="D25" s="63" t="str">
+      <c r="D25" s="78" t="str">
         <f>IF(AND('5-Year P&amp;L'!D24&gt;=0,'5-Year P&amp;L'!C24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="E25" s="63" t="str">
+      <c r="E25" s="78" t="str">
         <f>IF(AND('5-Year P&amp;L'!E24&gt;=0,'5-Year P&amp;L'!D24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="F25" s="63" t="str">
+      <c r="F25" s="78" t="str">
         <f>IF(AND('5-Year P&amp;L'!F24&gt;=0,'5-Year P&amp;L'!E24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="G25" s="63" t="str">
+      <c r="G25" s="78" t="str">
         <f>IF(AND('5-Year P&amp;L'!G24&gt;=0,'5-Year P&amp;L'!F24&lt;0),"✓ Break-even","")</f>
         <v>0</v>
       </c>
-      <c r="H25" s="58" t="s">
+      <c r="H25" s="73" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B26" s="28" t="s">
-        <v>227</v>
-      </c>
-      <c r="C26" s="64">
+        <v>261</v>
+      </c>
+      <c r="C26" s="79">
         <v>-7</v>
       </c>
-      <c r="D26" s="64">
+      <c r="D26" s="79">
         <v>-11</v>
       </c>
-      <c r="E26" s="64">
+      <c r="E26" s="79">
         <v>-16</v>
       </c>
-      <c r="F26" s="64">
+      <c r="F26" s="79">
         <v>-18</v>
       </c>
-      <c r="G26" s="64">
+      <c r="G26" s="79">
         <v>-22</v>
       </c>
-      <c r="H26" s="58" t="s">
-        <v>228</v>
+      <c r="H26" s="73" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B27" s="28" t="s">
-        <v>229</v>
-      </c>
-      <c r="C27" s="64">
-        <v>0</v>
-      </c>
-      <c r="D27" s="64">
-        <v>0</v>
-      </c>
-      <c r="E27" s="64">
-        <v>0</v>
-      </c>
-      <c r="F27" s="64">
-        <v>0</v>
-      </c>
-      <c r="G27" s="64">
-        <v>0</v>
-      </c>
-      <c r="H27" s="58" t="s">
-        <v>230</v>
+        <v>263</v>
+      </c>
+      <c r="C27" s="79">
+        <v>0</v>
+      </c>
+      <c r="D27" s="79">
+        <v>0</v>
+      </c>
+      <c r="E27" s="79">
+        <v>0</v>
+      </c>
+      <c r="F27" s="79">
+        <v>0</v>
+      </c>
+      <c r="G27" s="79">
+        <v>0</v>
+      </c>
+      <c r="H27" s="73" t="s">
+        <v>264</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B29" s="54" t="s">
-        <v>231</v>
-      </c>
-      <c r="C29" s="54" t="s">
-        <v>232</v>
-      </c>
-      <c r="D29" s="54" t="s">
-        <v>233</v>
-      </c>
-      <c r="E29" s="54"/>
-      <c r="F29" s="54" t="s">
-        <v>234</v>
-      </c>
-      <c r="G29" s="54"/>
-      <c r="H29" s="54"/>
-      <c r="I29" s="54"/>
+      <c r="B29" s="69" t="s">
+        <v>265</v>
+      </c>
+      <c r="C29" s="69" t="s">
+        <v>266</v>
+      </c>
+      <c r="D29" s="69" t="s">
+        <v>267</v>
+      </c>
+      <c r="E29" s="69"/>
+      <c r="F29" s="69" t="s">
+        <v>268</v>
+      </c>
+      <c r="G29" s="69"/>
+      <c r="H29" s="69"/>
+      <c r="I29" s="69"/>
     </row>
     <row r="30" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B30" s="65" t="s">
-        <v>235</v>
-      </c>
-      <c r="C30" s="66" t="s">
-        <v>236</v>
-      </c>
-      <c r="D30" s="67" t="s">
-        <v>237</v>
-      </c>
-      <c r="E30" s="67"/>
-      <c r="F30" s="68" t="s">
-        <v>238</v>
-      </c>
-      <c r="G30" s="68"/>
-      <c r="H30" s="68"/>
-      <c r="I30" s="68"/>
+      <c r="B30" s="80" t="s">
+        <v>269</v>
+      </c>
+      <c r="C30" s="81" t="s">
+        <v>270</v>
+      </c>
+      <c r="D30" s="82" t="s">
+        <v>271</v>
+      </c>
+      <c r="E30" s="82"/>
+      <c r="F30" s="83" t="s">
+        <v>272</v>
+      </c>
+      <c r="G30" s="83"/>
+      <c r="H30" s="83"/>
+      <c r="I30" s="83"/>
     </row>
     <row r="31" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B31" s="65" t="s">
-        <v>239</v>
-      </c>
-      <c r="C31" s="66" t="s">
-        <v>236</v>
-      </c>
-      <c r="D31" s="67" t="s">
-        <v>240</v>
-      </c>
-      <c r="E31" s="67"/>
-      <c r="F31" s="68" t="s">
-        <v>241</v>
-      </c>
-      <c r="G31" s="68"/>
-      <c r="H31" s="68"/>
-      <c r="I31" s="68"/>
+      <c r="B31" s="80" t="s">
+        <v>273</v>
+      </c>
+      <c r="C31" s="81" t="s">
+        <v>270</v>
+      </c>
+      <c r="D31" s="82" t="s">
+        <v>274</v>
+      </c>
+      <c r="E31" s="82"/>
+      <c r="F31" s="83" t="s">
+        <v>275</v>
+      </c>
+      <c r="G31" s="83"/>
+      <c r="H31" s="83"/>
+      <c r="I31" s="83"/>
     </row>
     <row r="32" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B32" s="65" t="s">
-        <v>242</v>
-      </c>
-      <c r="C32" s="66" t="s">
-        <v>236</v>
-      </c>
-      <c r="D32" s="67" t="s">
-        <v>243</v>
-      </c>
-      <c r="E32" s="67"/>
-      <c r="F32" s="68" t="s">
-        <v>244</v>
-      </c>
-      <c r="G32" s="68"/>
-      <c r="H32" s="68"/>
-      <c r="I32" s="68"/>
+      <c r="B32" s="80" t="s">
+        <v>276</v>
+      </c>
+      <c r="C32" s="81" t="s">
+        <v>270</v>
+      </c>
+      <c r="D32" s="82" t="s">
+        <v>277</v>
+      </c>
+      <c r="E32" s="82"/>
+      <c r="F32" s="83" t="s">
+        <v>278</v>
+      </c>
+      <c r="G32" s="83"/>
+      <c r="H32" s="83"/>
+      <c r="I32" s="83"/>
     </row>
     <row r="33" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B33" s="65" t="s">
-        <v>245</v>
-      </c>
-      <c r="C33" s="69" t="s">
-        <v>246</v>
-      </c>
-      <c r="D33" s="67" t="s">
-        <v>247</v>
-      </c>
-      <c r="E33" s="67"/>
-      <c r="F33" s="68" t="s">
-        <v>248</v>
-      </c>
-      <c r="G33" s="68"/>
-      <c r="H33" s="68"/>
-      <c r="I33" s="68"/>
+      <c r="B33" s="80" t="s">
+        <v>279</v>
+      </c>
+      <c r="C33" s="84" t="s">
+        <v>280</v>
+      </c>
+      <c r="D33" s="82" t="s">
+        <v>281</v>
+      </c>
+      <c r="E33" s="82"/>
+      <c r="F33" s="83" t="s">
+        <v>282</v>
+      </c>
+      <c r="G33" s="83"/>
+      <c r="H33" s="83"/>
+      <c r="I33" s="83"/>
     </row>
     <row r="34" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B34" s="65" t="s">
-        <v>249</v>
-      </c>
-      <c r="C34" s="66" t="s">
-        <v>236</v>
-      </c>
-      <c r="D34" s="67" t="s">
-        <v>250</v>
-      </c>
-      <c r="E34" s="67"/>
-      <c r="F34" s="68" t="s">
-        <v>251</v>
-      </c>
-      <c r="G34" s="68"/>
-      <c r="H34" s="68"/>
-      <c r="I34" s="68"/>
+      <c r="B34" s="80" t="s">
+        <v>283</v>
+      </c>
+      <c r="C34" s="81" t="s">
+        <v>270</v>
+      </c>
+      <c r="D34" s="82" t="s">
+        <v>284</v>
+      </c>
+      <c r="E34" s="82"/>
+      <c r="F34" s="83" t="s">
+        <v>285</v>
+      </c>
+      <c r="G34" s="83"/>
+      <c r="H34" s="83"/>
+      <c r="I34" s="83"/>
     </row>
     <row r="35" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B35" s="65" t="s">
-        <v>252</v>
-      </c>
-      <c r="C35" s="70" t="s">
-        <v>253</v>
-      </c>
-      <c r="D35" s="67" t="s">
-        <v>254</v>
-      </c>
-      <c r="E35" s="67"/>
-      <c r="F35" s="68" t="s">
-        <v>255</v>
-      </c>
-      <c r="G35" s="68"/>
-      <c r="H35" s="68"/>
-      <c r="I35" s="68"/>
+      <c r="B35" s="80" t="s">
+        <v>286</v>
+      </c>
+      <c r="C35" s="85" t="s">
+        <v>287</v>
+      </c>
+      <c r="D35" s="82" t="s">
+        <v>288</v>
+      </c>
+      <c r="E35" s="82"/>
+      <c r="F35" s="83" t="s">
+        <v>289</v>
+      </c>
+      <c r="G35" s="83"/>
+      <c r="H35" s="83"/>
+      <c r="I35" s="83"/>
     </row>
     <row r="36" ht="45" customHeight="1" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B36" s="65" t="s">
-        <v>256</v>
-      </c>
-      <c r="C36" s="66" t="s">
-        <v>236</v>
-      </c>
-      <c r="D36" s="67" t="s">
-        <v>257</v>
-      </c>
-      <c r="E36" s="67"/>
-      <c r="F36" s="68" t="s">
-        <v>258</v>
-      </c>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
-      <c r="I36" s="68"/>
+      <c r="B36" s="80" t="s">
+        <v>290</v>
+      </c>
+      <c r="C36" s="81" t="s">
+        <v>270</v>
+      </c>
+      <c r="D36" s="82" t="s">
+        <v>291</v>
+      </c>
+      <c r="E36" s="82"/>
+      <c r="F36" s="83" t="s">
+        <v>292</v>
+      </c>
+      <c r="G36" s="83"/>
+      <c r="H36" s="83"/>
+      <c r="I36" s="83"/>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="65" t="s">
+      <c r="B38" s="80" t="s">
         <v>39</v>
       </c>
       <c r="C38" s="28" t="s">
-        <v>259</v>
+        <v>293</v>
       </c>
       <c r="D38" s="28"/>
       <c r="E38" s="28"/>
       <c r="F38" s="28"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B40" s="71" t="s">
-        <v>260</v>
-      </c>
-      <c r="C40" s="71"/>
-      <c r="D40" s="71"/>
-      <c r="E40" s="71"/>
-      <c r="F40" s="71"/>
-      <c r="G40" s="71"/>
-      <c r="H40" s="71"/>
-      <c r="I40" s="71"/>
+      <c r="B40" s="86" t="s">
+        <v>294</v>
+      </c>
+      <c r="C40" s="86"/>
+      <c r="D40" s="86"/>
+      <c r="E40" s="86"/>
+      <c r="F40" s="86"/>
+      <c r="G40" s="86"/>
+      <c r="H40" s="86"/>
+      <c r="I40" s="86"/>
     </row>
   </sheetData>
   <mergeCells count="20">
@@ -3967,7 +5463,7 @@
     <tabColor rgb="FF328555"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:G25"/>
+  <dimension ref="B1:G26"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -4283,118 +5779,138 @@
         <v>125</v>
       </c>
       <c r="C19" s="27">
-        <f>'Cash Flow &amp; DSCR'!C9</f>
-        <v>6959.80855059</v>
+        <v>1656</v>
       </c>
       <c r="D19" s="27">
-        <f>'Cash Flow &amp; DSCR'!D9</f>
-        <v>6959.80855059</v>
+        <v>1329</v>
       </c>
       <c r="E19" s="27">
-        <f>'Cash Flow &amp; DSCR'!E9</f>
-        <v>6959.80855059</v>
+        <v>981</v>
       </c>
       <c r="F19" s="27">
-        <f>'Cash Flow &amp; DSCR'!F9</f>
-        <v>6959.80855059</v>
+        <v>613</v>
       </c>
       <c r="G19" s="27">
-        <f>'Cash Flow &amp; DSCR'!G9</f>
-        <v>6959.80855059</v>
-      </c>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B21" s="28" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B20" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="C21" s="30">
-        <f>C16-C19</f>
+      <c r="C20" s="27">
+        <f>'Cash Flow &amp; DSCR'!C9-C19</f>
+        <v>5304.09501734</v>
+      </c>
+      <c r="D20" s="27">
+        <f>'Cash Flow &amp; DSCR'!D9-D19</f>
+        <v>5631.23999193</v>
+      </c>
+      <c r="E20" s="27">
+        <f>'Cash Flow &amp; DSCR'!E9-E19</f>
+        <v>5978.56255272</v>
+      </c>
+      <c r="F20" s="27">
+        <f>'Cash Flow &amp; DSCR'!F9-F19</f>
+        <v>6347.30720906</v>
+      </c>
+      <c r="G20" s="27">
+        <f>'Cash Flow &amp; DSCR'!G9-G19</f>
+        <v>6738.79522895</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B22" s="28" t="s">
+        <v>127</v>
+      </c>
+      <c r="C22" s="30">
+        <f>C16-C19-C20</f>
         <v>-120159.80855059</v>
       </c>
-      <c r="D21" s="30">
-        <f>D16-D19</f>
+      <c r="D22" s="30">
+        <f>D16-D19-D20</f>
         <v>-135099.80855059</v>
       </c>
-      <c r="E21" s="30">
-        <f>E16-E19</f>
+      <c r="E22" s="30">
+        <f>E16-E19-E20</f>
         <v>-123705.81182332</v>
       </c>
-      <c r="F21" s="30">
-        <f>F16-F19</f>
+      <c r="F22" s="30">
+        <f>F16-F19-F20</f>
         <v>-174450.70700751</v>
       </c>
-      <c r="G21" s="30">
-        <f>G16-G19</f>
+      <c r="G22" s="30">
+        <f>G16-G19-G20</f>
         <v>-207461.80311556</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B22" s="25" t="s">
-        <v>127</v>
-      </c>
-      <c r="C22" s="31">
-        <f>IF(C10&gt;0,C21/C10,0)</f>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B23" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="31">
+        <f>IF(C10&gt;0,C22/C10,0)</f>
         <v>-1.35011021</v>
       </c>
-      <c r="D22" s="31">
-        <f>IF(D10&gt;0,D21/D10,0)</f>
+      <c r="D23" s="31">
+        <f>IF(D10&gt;0,D22/D10,0)</f>
         <v>-1.00237282</v>
       </c>
-      <c r="E22" s="31">
-        <f>IF(E10&gt;0,E21/E10,0)</f>
+      <c r="E23" s="31">
+        <f>IF(E10&gt;0,E22/E10,0)</f>
         <v>-0.73468845</v>
       </c>
-      <c r="F22" s="31">
-        <f>IF(F10&gt;0,F21/F10,0)</f>
+      <c r="F23" s="31">
+        <f>IF(F10&gt;0,F22/F10,0)</f>
         <v>-0.88902397</v>
       </c>
-      <c r="G22" s="31">
-        <f>IF(G10&gt;0,G21/G10,0)</f>
+      <c r="G23" s="31">
+        <f>IF(G10&gt;0,G22/G10,0)</f>
         <v>-1.02722149</v>
-      </c>
-    </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.25">
-      <c r="B24" s="28" t="s">
-        <v>128</v>
-      </c>
-      <c r="C24" s="32">
-        <f>C21</f>
-        <v>-120159.80855059</v>
-      </c>
-      <c r="D24" s="32">
-        <f>C24+D21</f>
-        <v>-255259.61710119</v>
-      </c>
-      <c r="E24" s="32">
-        <f>D24+E21</f>
-        <v>-378965.42892451</v>
-      </c>
-      <c r="F24" s="32">
-        <f>E24+F21</f>
-        <v>-553416.13593202</v>
-      </c>
-      <c r="G24" s="32">
-        <f>F24+G21</f>
-        <v>-760877.93904758</v>
       </c>
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="28" t="s">
         <v>129</v>
       </c>
-      <c r="C25" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="D25" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="E25" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="F25" s="33" t="s">
-        <v>7</v>
-      </c>
-      <c r="G25" s="33" t="s">
+      <c r="C25" s="32">
+        <f>C22</f>
+        <v>-120159.80855059</v>
+      </c>
+      <c r="D25" s="32">
+        <f>C25+D22</f>
+        <v>-255259.61710119</v>
+      </c>
+      <c r="E25" s="32">
+        <f>D25+E22</f>
+        <v>-378965.42892451</v>
+      </c>
+      <c r="F25" s="32">
+        <f>E25+F22</f>
+        <v>-553416.13593202</v>
+      </c>
+      <c r="G25" s="32">
+        <f>F25+G22</f>
+        <v>-760877.93904758</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B26" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="E26" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="F26" s="33" t="s">
+        <v>7</v>
+      </c>
+      <c r="G26" s="33" t="s">
         <v>7</v>
       </c>
     </row>
@@ -4426,7 +5942,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -4454,7 +5970,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="28" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C4" s="32" t="str">
         <f>Assumptions!D57</f>
@@ -4479,7 +5995,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="25" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C5" s="27">
         <f>'5-Year P&amp;L'!C16</f>
@@ -4504,7 +6020,7 @@
     </row>
     <row r="7" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B7" s="25" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C7" s="27" t="str">
         <f>Assumptions!D58</f>
@@ -4529,7 +6045,7 @@
     </row>
     <row r="8" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C8" s="27">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -4554,7 +6070,7 @@
     </row>
     <row r="9" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B9" s="28" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C9" s="29">
         <f>C7+C8</f>
@@ -4579,7 +6095,7 @@
     </row>
     <row r="11" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B11" s="28" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C11" s="34">
         <f>IF(C9&gt;0,C5/C9,IF(C5&gt;0,99.9,0))</f>
@@ -4604,7 +6120,7 @@
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B13" s="25" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C13" s="27">
         <f>C5-C9</f>
@@ -4629,7 +6145,7 @@
     </row>
     <row r="14" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B14" s="28" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C14" s="32">
         <f>C5-C9</f>
@@ -4654,7 +6170,7 @@
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B16" s="28" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C16" s="30">
         <f>C4+C14</f>
@@ -4692,6 +6208,267 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor rgb="FF7C3AED"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="B1:G17"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+  <cols>
+    <col min="1" max="1" width="3" customWidth="1"/>
+    <col min="2" max="2" width="36" customWidth="1"/>
+    <col min="3" max="7" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B1" s="13" t="s">
+        <v>141</v>
+      </c>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+    </row>
+    <row r="2" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B2" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C2" s="3"/>
+      <c r="D2" s="3"/>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3"/>
+      <c r="G2" s="3"/>
+    </row>
+    <row r="4" ht="24" customHeight="1" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="23"/>
+      <c r="C4" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="F4" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="G4" s="24" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="35"/>
+      <c r="D5" s="35"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="35"/>
+      <c r="G5" s="35"/>
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B6" s="25" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" s="27">
+        <v>0</v>
+      </c>
+      <c r="D6" s="27">
+        <v>0</v>
+      </c>
+      <c r="E6" s="27">
+        <v>0</v>
+      </c>
+      <c r="F6" s="27">
+        <v>0</v>
+      </c>
+      <c r="G6" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B7" s="25" t="s">
+        <v>145</v>
+      </c>
+      <c r="C7" s="27">
+        <v>0</v>
+      </c>
+      <c r="D7" s="27">
+        <v>0</v>
+      </c>
+      <c r="E7" s="27">
+        <v>0</v>
+      </c>
+      <c r="F7" s="27">
+        <v>0</v>
+      </c>
+      <c r="G7" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B8" s="28" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="36" t="str">
+        <f>C6-C7</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="36" t="str">
+        <f>D6-D7</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="36" t="str">
+        <f>E6-E7</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="36" t="str">
+        <f>F6-F7</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="36" t="str">
+        <f>G6-G7</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B9" s="28" t="s">
+        <v>147</v>
+      </c>
+      <c r="C9" s="29" t="str">
+        <f>C7*30/365</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="29" t="str">
+        <f>D7*30/365</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="29" t="str">
+        <f>E7*30/365</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="29" t="str">
+        <f>F7*30/365</f>
+        <v>0</v>
+      </c>
+      <c r="G9" s="29" t="str">
+        <f>G7*30/365</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B11" s="35" t="s">
+        <v>148</v>
+      </c>
+      <c r="C11" s="35"/>
+      <c r="D11" s="35"/>
+      <c r="E11" s="35"/>
+      <c r="F11" s="35"/>
+      <c r="G11" s="35"/>
+    </row>
+    <row r="12" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B12" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="C12" s="27">
+        <v>-120159.80855059417</v>
+      </c>
+      <c r="D12" s="27">
+        <v>-255259.61710118834</v>
+      </c>
+      <c r="E12" s="27">
+        <v>-378965.42892450973</v>
+      </c>
+      <c r="F12" s="27">
+        <v>-553416.1359320199</v>
+      </c>
+      <c r="G12" s="27">
+        <v>-760877.9390475792</v>
+      </c>
+    </row>
+    <row r="13" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B13" s="25" t="s">
+        <v>150</v>
+      </c>
+      <c r="C13" s="27">
+        <v>0</v>
+      </c>
+      <c r="D13" s="27">
+        <v>0</v>
+      </c>
+      <c r="E13" s="27">
+        <v>0</v>
+      </c>
+      <c r="F13" s="27">
+        <v>0</v>
+      </c>
+      <c r="G13" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B14" s="28" t="s">
+        <v>151</v>
+      </c>
+      <c r="C14" s="30">
+        <f>C12-C13</f>
+        <v>-120159.80855059</v>
+      </c>
+      <c r="D14" s="30">
+        <f>D12-D13</f>
+        <v>-255259.61710119</v>
+      </c>
+      <c r="E14" s="30">
+        <f>E12-E13</f>
+        <v>-378965.42892451</v>
+      </c>
+      <c r="F14" s="30">
+        <f>F12-F13</f>
+        <v>-553416.13593202</v>
+      </c>
+      <c r="G14" s="30">
+        <f>G12-G13</f>
+        <v>-760877.93904758</v>
+      </c>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B16" s="37" t="s">
+        <v>152</v>
+      </c>
+      <c r="C16" s="37"/>
+      <c r="D16" s="37"/>
+      <c r="E16" s="37"/>
+      <c r="F16" s="37"/>
+      <c r="G16" s="37"/>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.25">
+      <c r="B17" s="37"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="37"/>
+      <c r="E17" s="37"/>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="B2:G2"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B11:G11"/>
+    <mergeCell ref="B16:G17"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
+  <headerFooter>
+    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor rgb="FF0D9488"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -4705,7 +6482,7 @@
   <sheetData>
     <row r="1" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>140</v>
+        <v>153</v>
       </c>
       <c r="C1" s="13"/>
       <c r="D1" s="13"/>
@@ -4733,7 +6510,7 @@
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
-        <v>141</v>
+        <v>154</v>
       </c>
       <c r="C4" s="26">
         <f>Drivers!C12</f>
@@ -4758,7 +6535,7 @@
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B5" s="25" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="C5" s="26">
         <f>Assumptions!D35</f>
@@ -4783,25 +6560,25 @@
     </row>
     <row r="6" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B6" s="28" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="35">
+        <v>156</v>
+      </c>
+      <c r="C6" s="38">
         <f>C4+C5</f>
         <v>3</v>
       </c>
-      <c r="D6" s="35">
+      <c r="D6" s="38">
         <f>D4+D5</f>
         <v>4</v>
       </c>
-      <c r="E6" s="35">
+      <c r="E6" s="38">
         <f>E4+E5</f>
         <v>4</v>
       </c>
-      <c r="F6" s="35">
+      <c r="F6" s="38">
         <f>F4+F5</f>
         <v>5</v>
       </c>
-      <c r="G6" s="35">
+      <c r="G6" s="38">
         <f>G4+G5</f>
         <v>5</v>
       </c>
@@ -4818,7 +6595,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFD97706"/>
@@ -4834,13 +6611,13 @@
   <sheetData>
     <row r="1" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B1" s="13" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="C1" s="13"/>
     </row>
     <row r="3" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B3" s="25" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="C3" s="27">
         <f>Assumptions!D59</f>
@@ -4849,7 +6626,7 @@
     </row>
     <row r="4" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B4" s="25" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="C4" s="31">
         <f>Assumptions!D60</f>
@@ -4867,7 +6644,7 @@
     </row>
     <row r="6" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B6" s="25" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="C6" s="32">
         <f>IF(Assumptions!D59&gt;0,PMT(Assumptions!D60/12,Assumptions!D61*12,-Assumptions!D59)*12,0)</f>
@@ -4876,7 +6653,7 @@
     </row>
     <row r="8" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B8" s="25" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="C8" s="34">
         <f>'Cash Flow &amp; DSCR'!C11</f>
@@ -4893,174 +6670,4 @@
     <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <sheetPr>
-    <tabColor rgb="FF328555"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="B1:C21"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
-  <cols>
-    <col min="1" max="1" width="3" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="13" t="s">
-        <v>149</v>
-      </c>
-      <c r="C1" s="13"/>
-    </row>
-    <row r="3" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B3" s="25" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="25" t="str">
-        <f>Assumptions!D5</f>
-        <v>Bright Horizons Microschool</v>
-      </c>
-    </row>
-    <row r="4" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B4" s="25" t="s">
-        <v>49</v>
-      </c>
-      <c r="C4" s="25" t="str">
-        <f>Assumptions!D7</f>
-        <v>Microschool</v>
-      </c>
-    </row>
-    <row r="5" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B5" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" s="25" t="str">
-        <f>Assumptions!D6</f>
-        <v>AZ</v>
-      </c>
-    </row>
-    <row r="6" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B6" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="C6" s="25">
-        <f>Assumptions!D8</f>
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="8" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B8" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="C8" s="26">
-        <f>Assumptions!D16</f>
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B9" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="C9" s="27">
-        <f>Drivers!G10</f>
-        <v>201964.04175</v>
-      </c>
-    </row>
-    <row r="10" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B10" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="C10" s="36">
-        <f>'5-Year P&amp;L'!G16</f>
-        <v>-200501.99456497</v>
-      </c>
-    </row>
-    <row r="12" ht="24" customHeight="1" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B12" s="37" t="s">
-        <v>153</v>
-      </c>
-      <c r="C12" s="23"/>
-    </row>
-    <row r="13" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B13" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="C13" s="38">
-        <f>IF(Drivers!G10&gt;0,'5-Year P&amp;L'!G21/Drivers!G10,0)</f>
-        <v>-1.02722149</v>
-      </c>
-    </row>
-    <row r="14" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B14" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="C14" s="31">
-        <f>IF(Drivers!G10&gt;0,Drivers!G16/Drivers!G10,0)</f>
-        <v>1.34416366</v>
-      </c>
-    </row>
-    <row r="15" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B15" s="25" t="s">
-        <v>156</v>
-      </c>
-      <c r="C15" s="27">
-        <f>IF(Assumptions!D16&gt;0,Drivers!G10/Assumptions!D16,0)</f>
-        <v>8079</v>
-      </c>
-    </row>
-    <row r="16" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B16" s="25" t="s">
-        <v>157</v>
-      </c>
-      <c r="C16" s="27">
-        <f>IF(Assumptions!D16&gt;0,('5-Year P&amp;L'!G12+'5-Year P&amp;L'!G13)/Assumptions!D16,0)</f>
-        <v>16099</v>
-      </c>
-    </row>
-    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B17" s="25" t="s">
-        <v>158</v>
-      </c>
-      <c r="C17" s="34">
-        <f>'Cash Flow &amp; DSCR'!C11</f>
-        <v>-16.26481521</v>
-      </c>
-    </row>
-    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B18" s="25" t="s">
-        <v>159</v>
-      </c>
-      <c r="C18" s="34">
-        <f>'Cash Flow &amp; DSCR'!G11</f>
-        <v>-28.80855028</v>
-      </c>
-    </row>
-    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B19" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="C19" s="39">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B21" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="C21" s="12"/>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B21:C21"/>
-  </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="landscape" fitToWidth="1" fitToHeight="0"/>
-  <headerFooter>
-    <oddFooter>&amp;L&amp;8SchoolStack Budget&amp;C&amp;8Confidential&amp;R&amp;8Page &amp;P of &amp;N</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>